--- a/registration_forms/025_preschool_checklist_form--registration_forms.xlsx
+++ b/registration_forms/025_preschool_checklist_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -880,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1095,34 +1095,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>classroom_supplies_choices</t>
+          <t>educational_materials_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>folders</t>
+          <t>math_books</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>folders</t>
+          <t>math books</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>classroom_supplies_choices</t>
+          <t>educational_materials_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>folders</t>
+          <t>reading_materials</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>folders</t>
+          <t>reading materials</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>math_books</t>
+          <t>art_supplies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>math_books</t>
+          <t>art supplies</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>reading_materials</t>
+          <t>craft_supplies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>reading_materials</t>
+          <t>craft supplies</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>art_supplies</t>
+          <t>music_instruments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>art_supplies</t>
+          <t>music instruments</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>craft_supplies</t>
+          <t>computers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>craft_supplies</t>
+          <t>computers</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>music_instruments</t>
+          <t>tablets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>music_instruments</t>
+          <t>tablets</t>
         </is>
       </c>
     </row>
@@ -1219,46 +1219,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>computers</t>
+          <t>classroom_decorations</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>computers</t>
+          <t>classroom decorations</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>educational_materials_choices</t>
+          <t>classroom_equipment_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tablets</t>
+          <t>chairs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tablets</t>
+          <t>chairs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>educational_materials_choices</t>
+          <t>classroom_equipment_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>classroom_decorations</t>
+          <t>table</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>classroom_decorations</t>
+          <t>table</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>chairs</t>
+          <t>whiteboard</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>chairs</t>
+          <t>whiteboard</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>projector</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>table</t>
+          <t>projector</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>whiteboard</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>whiteboard</t>
+          <t>mic</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>projector</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>projector</t>
+          <t>speaker</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mic</t>
+          <t>bookshelf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mic</t>
+          <t>bookshelf</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>shelves</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>speaker</t>
+          <t>shelves</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>bookshelf</t>
+          <t>filing_cabinet</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bookshelf</t>
+          <t>filing cabinet</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>shelves</t>
+          <t>computer_station</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>shelves</t>
+          <t>computer station</t>
         </is>
       </c>
     </row>
@@ -1406,46 +1406,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>filing_cabinet</t>
+          <t>water_station</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>filing_cabinet</t>
+          <t>water station</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>classroom_equipment_choices</t>
+          <t>activity_schedule_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>computer_station</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>computer_station</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>classroom_equipment_choices</t>
+          <t>activity_schedule_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>water_station</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>water_station</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1525,46 +1525,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>activity_schedule_choices</t>
+          <t>school_term_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Fall</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>activity_schedule_choices</t>
+          <t>school_term_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sunday</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1593,78 +1593,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>year-round</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Year-round</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>school_term_choices</t>
+          <t>parent_signature_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>summer</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>school_term_choices</t>
+          <t>parent_signature_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>year-round</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>Year-round</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>parent_signature_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>parent_signature_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
         <is>
           <t>False</t>
         </is>
